--- a/database/event/5864/event_5864_evp_summary.xlsx
+++ b/database/event/5864/event_5864_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9568</v>
+        <v>5.7921</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1163</v>
+        <v>2.0578</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9851</v>
+        <v>1.8637</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9568</v>
+        <v>5.7921</v>
       </c>
       <c r="F2" t="n">
-        <v>5.9568</v>
+        <v>5.7921</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.0372</v>
+        <v>6.779</v>
       </c>
       <c r="I2" t="n">
         <v>7.3716</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.532</v>
+        <v>5.3829</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9654</v>
+        <v>1.9124</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8134</v>
+        <v>1.7006</v>
       </c>
       <c r="E3" t="n">
-        <v>5.532</v>
+        <v>5.3829</v>
       </c>
       <c r="F3" t="n">
-        <v>5.532</v>
+        <v>5.3829</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6.3711</v>
+        <v>6.1374</v>
       </c>
       <c r="I3" t="n">
         <v>6.6739</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3187</v>
+        <v>5.1499</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8896</v>
+        <v>1.8296</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7273</v>
+        <v>1.6078</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3187</v>
+        <v>5.1499</v>
       </c>
       <c r="F4" t="n">
-        <v>5.3187</v>
+        <v>5.1499</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6.0367</v>
+        <v>5.7719</v>
       </c>
       <c r="I4" t="n">
         <v>6.3826</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0388</v>
+        <v>4.8822</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7901</v>
+        <v>1.7345</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6142</v>
+        <v>1.5012</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0388</v>
+        <v>4.8822</v>
       </c>
       <c r="F5" t="n">
-        <v>5.0388</v>
+        <v>4.8822</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5978</v>
+        <v>5.3523</v>
       </c>
       <c r="I5" t="n">
         <v>5.9186</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5337</v>
+        <v>4.4212</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6107</v>
+        <v>1.5707</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4102</v>
+        <v>1.3175</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5337</v>
+        <v>4.4212</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5337</v>
+        <v>4.4212</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8058</v>
+        <v>4.6295</v>
       </c>
       <c r="I6" t="n">
         <v>5.0342</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.4715</v>
+        <v>4.3939</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5886</v>
+        <v>1.561</v>
       </c>
       <c r="D7" t="n">
-        <v>1.385</v>
+        <v>1.3066</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4715</v>
+        <v>4.3939</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4715</v>
+        <v>4.3939</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7082</v>
+        <v>4.5867</v>
       </c>
       <c r="I7" t="n">
         <v>4.8638</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3825</v>
+        <v>4.3178</v>
       </c>
       <c r="C8" t="n">
-        <v>1.557</v>
+        <v>1.534</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3491</v>
+        <v>1.2763</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3825</v>
+        <v>4.3178</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3825</v>
+        <v>4.3178</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5686</v>
+        <v>4.4673</v>
       </c>
       <c r="I8" t="n">
         <v>4.6977</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.2966</v>
+        <v>4.2235</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5265</v>
+        <v>1.5005</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3144</v>
+        <v>1.2387</v>
       </c>
       <c r="E9" t="n">
-        <v>4.2966</v>
+        <v>4.2235</v>
       </c>
       <c r="F9" t="n">
-        <v>4.2966</v>
+        <v>4.2235</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.434</v>
+        <v>4.3195</v>
       </c>
       <c r="I9" t="n">
         <v>4.5805</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1282</v>
+        <v>4.0692</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4666</v>
+        <v>1.4457</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2463</v>
+        <v>1.1773</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1282</v>
+        <v>4.0692</v>
       </c>
       <c r="F10" t="n">
-        <v>4.1282</v>
+        <v>4.0692</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.17</v>
+        <v>4.0775</v>
       </c>
       <c r="I10" t="n">
         <v>4.2878</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.0659</v>
+        <v>3.9255</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4445</v>
+        <v>1.3946</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2212</v>
+        <v>1.12</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0659</v>
+        <v>3.9255</v>
       </c>
       <c r="F11" t="n">
-        <v>4.0659</v>
+        <v>3.9255</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4.0723</v>
+        <v>3.9255</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2658</v>
+        <v>4.2331</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>287</v>
+        <v>437</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2658</v>
+        <v>4.2331</v>
       </c>
       <c r="N11" t="n">
-        <v>287</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.058</v>
+        <v>3.9229</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4417</v>
+        <v>1.3937</v>
       </c>
       <c r="D12" t="n">
-        <v>1.218</v>
+        <v>1.119</v>
       </c>
       <c r="E12" t="n">
-        <v>4.058</v>
+        <v>3.9229</v>
       </c>
       <c r="F12" t="n">
-        <v>4.058</v>
+        <v>3.9229</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.0598</v>
+        <v>3.9229</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2331</v>
+        <v>4.2658</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>437</v>
+        <v>287</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2331</v>
+        <v>4.2658</v>
       </c>
       <c r="N12" t="n">
-        <v>437</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13">
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.0196</v>
+        <v>3.8721</v>
       </c>
       <c r="C13" t="n">
-        <v>1.428</v>
+        <v>1.3756</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2025</v>
+        <v>1.0987</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0196</v>
+        <v>3.8721</v>
       </c>
       <c r="F13" t="n">
-        <v>4.0196</v>
+        <v>3.8721</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4.0196</v>
+        <v>3.8721</v>
       </c>
       <c r="I13" t="n">
         <v>4.2106</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.9071</v>
+        <v>3.8062</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3881</v>
+        <v>1.3522</v>
       </c>
       <c r="D14" t="n">
-        <v>1.157</v>
+        <v>1.0725</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9071</v>
+        <v>3.8062</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9071</v>
+        <v>3.8062</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9071</v>
+        <v>3.8062</v>
       </c>
       <c r="I14" t="n">
         <v>4.0362</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.6228</v>
+        <v>3.5425</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2871</v>
+        <v>1.2585</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0422</v>
+        <v>0.9674</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6228</v>
+        <v>3.5425</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6228</v>
+        <v>3.5425</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6228</v>
+        <v>3.5425</v>
       </c>
       <c r="I15" t="n">
         <v>3.7252</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.5375</v>
+        <v>3.4462</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2568</v>
+        <v>1.2243</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0077</v>
+        <v>0.9291</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5375</v>
+        <v>3.4462</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5375</v>
+        <v>3.4462</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5375</v>
+        <v>3.4462</v>
       </c>
       <c r="I16" t="n">
         <v>3.6544</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.4714</v>
+        <v>3.3441</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2333</v>
+        <v>1.1881</v>
       </c>
       <c r="D17" t="n">
-        <v>0.981</v>
+        <v>0.8884</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4714</v>
+        <v>3.3441</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4714</v>
+        <v>3.3441</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4714</v>
+        <v>3.3441</v>
       </c>
       <c r="I17" t="n">
         <v>3.6364</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.402</v>
+        <v>3.2903</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2086</v>
+        <v>1.1689</v>
       </c>
       <c r="D18" t="n">
-        <v>0.953</v>
+        <v>0.8669</v>
       </c>
       <c r="E18" t="n">
-        <v>3.402</v>
+        <v>3.2903</v>
       </c>
       <c r="F18" t="n">
-        <v>3.402</v>
+        <v>3.2903</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.402</v>
+        <v>3.2903</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5637</v>
+        <v>3.46</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>391</v>
+        <v>307</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5637</v>
+        <v>3.46</v>
       </c>
       <c r="N18" t="n">
-        <v>391</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.3649</v>
+        <v>3.2772</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1955</v>
+        <v>1.1643</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.8617</v>
       </c>
       <c r="E19" t="n">
-        <v>3.3649</v>
+        <v>3.2772</v>
       </c>
       <c r="F19" t="n">
-        <v>3.3649</v>
+        <v>3.2772</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.3649</v>
+        <v>3.2772</v>
       </c>
       <c r="I19" t="n">
-        <v>3.46</v>
+        <v>3.5637</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>307</v>
+        <v>391</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.46</v>
+        <v>3.5637</v>
       </c>
       <c r="N19" t="n">
-        <v>307</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20">
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.1539</v>
+        <v>3.0725</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1205</v>
+        <v>1.0916</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8527</v>
+        <v>0.7802</v>
       </c>
       <c r="E20" t="n">
-        <v>3.1539</v>
+        <v>3.0725</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1539</v>
+        <v>3.0725</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.1539</v>
+        <v>3.0725</v>
       </c>
       <c r="I20" t="n">
         <v>3.2581</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.1493</v>
+        <v>3.0679</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1189</v>
+        <v>1.0899</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8509</v>
+        <v>0.7783</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1493</v>
+        <v>3.0679</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1493</v>
+        <v>3.0679</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.1493</v>
+        <v>3.0679</v>
       </c>
       <c r="I21" t="n">
         <v>3.2533</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.1013</v>
+        <v>2.9988</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1018</v>
+        <v>1.0654</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8315</v>
+        <v>0.7508</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1013</v>
+        <v>2.9988</v>
       </c>
       <c r="F22" t="n">
-        <v>3.1013</v>
+        <v>2.9988</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1013</v>
+        <v>2.9988</v>
       </c>
       <c r="I22" t="n">
         <v>3.2337</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.9908</v>
+        <v>2.8918</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0625</v>
+        <v>1.0274</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7869</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>2.9908</v>
+        <v>2.8918</v>
       </c>
       <c r="F23" t="n">
-        <v>2.9908</v>
+        <v>2.8918</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.9908</v>
+        <v>2.8918</v>
       </c>
       <c r="I23" t="n">
         <v>3.1184</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.7257</v>
+        <v>2.6257</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9684</v>
+        <v>0.9328</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6798</v>
+        <v>0.6022</v>
       </c>
       <c r="E24" t="n">
-        <v>2.7257</v>
+        <v>2.6257</v>
       </c>
       <c r="F24" t="n">
-        <v>2.7257</v>
+        <v>2.6257</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7257</v>
+        <v>2.6257</v>
       </c>
       <c r="I24" t="n">
         <v>2.8552</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.4026</v>
+        <v>2.3581</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8536</v>
+        <v>0.8378</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5492</v>
+        <v>0.4956</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4026</v>
+        <v>2.3581</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4026</v>
+        <v>2.3581</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.4026</v>
+        <v>2.3581</v>
       </c>
       <c r="I25" t="n">
         <v>2.4591</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.3584</v>
+        <v>2.2718</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8379</v>
+        <v>0.8071</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5314</v>
+        <v>0.4612</v>
       </c>
       <c r="E26" t="n">
-        <v>2.3584</v>
+        <v>2.2718</v>
       </c>
       <c r="F26" t="n">
-        <v>2.3584</v>
+        <v>2.2718</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.3584</v>
+        <v>2.2718</v>
       </c>
       <c r="I26" t="n">
         <v>2.4704</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.2314</v>
+        <v>2.1901</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7781</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4801</v>
+        <v>0.4286</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2314</v>
+        <v>2.1901</v>
       </c>
       <c r="F27" t="n">
-        <v>2.2314</v>
+        <v>2.1901</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.2314</v>
+        <v>2.1901</v>
       </c>
       <c r="I27" t="n">
         <v>2.2838</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.0489</v>
+        <v>2.0109</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7279</v>
+        <v>0.7144</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4063</v>
+        <v>0.3572</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0489</v>
+        <v>2.0109</v>
       </c>
       <c r="F28" t="n">
-        <v>2.0489</v>
+        <v>2.0109</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.0489</v>
+        <v>2.0109</v>
       </c>
       <c r="I28" t="n">
         <v>2.097</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9332</v>
+        <v>1.8974</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6868</v>
+        <v>0.6741</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3596</v>
+        <v>0.312</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9332</v>
+        <v>1.8974</v>
       </c>
       <c r="F29" t="n">
-        <v>1.9332</v>
+        <v>1.8974</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.9332</v>
+        <v>1.8974</v>
       </c>
       <c r="I29" t="n">
         <v>1.9786</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.8672</v>
+        <v>1.8586</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6634</v>
+        <v>0.6603</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3329</v>
+        <v>0.2966</v>
       </c>
       <c r="E30" t="n">
-        <v>1.8672</v>
+        <v>1.8586</v>
       </c>
       <c r="F30" t="n">
-        <v>1.8672</v>
+        <v>1.8586</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.8672</v>
+        <v>1.8586</v>
       </c>
       <c r="I30" t="n">
-        <v>1.9199</v>
+        <v>1.8742</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>307</v>
+        <v>134</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.9199</v>
+        <v>1.8742</v>
       </c>
       <c r="N30" t="n">
-        <v>307</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.8655</v>
+        <v>1.8258</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3323</v>
+        <v>0.2835</v>
       </c>
       <c r="E31" t="n">
-        <v>1.8655</v>
+        <v>1.8258</v>
       </c>
       <c r="F31" t="n">
-        <v>1.8655</v>
+        <v>1.8258</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.8655</v>
+        <v>1.8258</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8742</v>
+        <v>1.9199</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>134</v>
+        <v>307</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.8742</v>
+        <v>1.9199</v>
       </c>
       <c r="N31" t="n">
-        <v>134</v>
+        <v>307</v>
       </c>
     </row>
     <row r="32">
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.8598</v>
+        <v>1.8118</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6607</v>
+        <v>0.6437</v>
       </c>
       <c r="D32" t="n">
-        <v>0.33</v>
+        <v>0.2779</v>
       </c>
       <c r="E32" t="n">
-        <v>1.8598</v>
+        <v>1.8118</v>
       </c>
       <c r="F32" t="n">
-        <v>1.8598</v>
+        <v>1.8118</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.8598</v>
+        <v>1.8118</v>
       </c>
       <c r="I32" t="n">
         <v>1.9212</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.7188</v>
+        <v>1.6807</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6106</v>
+        <v>0.5971</v>
       </c>
       <c r="D33" t="n">
-        <v>0.273</v>
+        <v>0.2257</v>
       </c>
       <c r="E33" t="n">
-        <v>1.7188</v>
+        <v>1.6807</v>
       </c>
       <c r="F33" t="n">
-        <v>1.7188</v>
+        <v>1.6807</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.7188</v>
+        <v>1.6807</v>
       </c>
       <c r="I33" t="n">
         <v>1.7673</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.6051</v>
+        <v>1.5636</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5702</v>
+        <v>0.5555</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2271</v>
+        <v>0.179</v>
       </c>
       <c r="E34" t="n">
-        <v>1.6051</v>
+        <v>1.5636</v>
       </c>
       <c r="F34" t="n">
-        <v>1.6051</v>
+        <v>1.5636</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.6051</v>
+        <v>1.5636</v>
       </c>
       <c r="I34" t="n">
         <v>1.6581</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.4584</v>
+        <v>1.3944</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5181</v>
+        <v>0.4954</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1678</v>
+        <v>0.1116</v>
       </c>
       <c r="E35" t="n">
-        <v>1.4584</v>
+        <v>1.3944</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4584</v>
+        <v>1.3944</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.4584</v>
+        <v>1.3944</v>
       </c>
       <c r="I35" t="n">
         <v>1.5419</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.3794</v>
+        <v>1.3189</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4901</v>
+        <v>0.4686</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1359</v>
+        <v>0.0815</v>
       </c>
       <c r="E36" t="n">
-        <v>1.3794</v>
+        <v>1.3189</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3794</v>
+        <v>1.3189</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.3794</v>
+        <v>1.3189</v>
       </c>
       <c r="I36" t="n">
         <v>1.4585</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.31</v>
+        <v>1.3002</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4654</v>
+        <v>0.4619</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1078</v>
+        <v>0.0741</v>
       </c>
       <c r="E37" t="n">
-        <v>1.31</v>
+        <v>1.3002</v>
       </c>
       <c r="F37" t="n">
-        <v>1.31</v>
+        <v>1.3002</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.31</v>
+        <v>1.3002</v>
       </c>
       <c r="I37" t="n">
         <v>1.3222</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.2124</v>
+        <v>1.1855</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4307</v>
+        <v>0.4212</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0684</v>
+        <v>0.0284</v>
       </c>
       <c r="E38" t="n">
-        <v>1.2124</v>
+        <v>1.1855</v>
       </c>
       <c r="F38" t="n">
-        <v>1.2124</v>
+        <v>1.1855</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.2124</v>
+        <v>1.1855</v>
       </c>
       <c r="I38" t="n">
         <v>1.2466</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.2103</v>
+        <v>1.1835</v>
       </c>
       <c r="C39" t="n">
-        <v>0.43</v>
+        <v>0.4205</v>
       </c>
       <c r="D39" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0276</v>
       </c>
       <c r="E39" t="n">
-        <v>1.2103</v>
+        <v>1.1835</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2103</v>
+        <v>1.1835</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.2103</v>
+        <v>1.1835</v>
       </c>
       <c r="I39" t="n">
         <v>1.2445</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.1666</v>
+        <v>1.145</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4145</v>
+        <v>0.4068</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0499</v>
+        <v>0.0123</v>
       </c>
       <c r="E40" t="n">
-        <v>1.1666</v>
+        <v>1.145</v>
       </c>
       <c r="F40" t="n">
-        <v>1.1666</v>
+        <v>1.145</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.1666</v>
+        <v>1.145</v>
       </c>
       <c r="I40" t="n">
         <v>1.194</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8451</v>
+        <v>0.8294</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3002</v>
+        <v>0.2947</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.08</v>
+        <v>-0.1135</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8451</v>
+        <v>0.8294</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8451</v>
+        <v>0.8294</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8451</v>
+        <v>0.8294</v>
       </c>
       <c r="I41" t="n">
         <v>0.8649</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7431</v>
+        <v>0.7375</v>
       </c>
       <c r="C42" t="n">
-        <v>0.264</v>
+        <v>0.262</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1212</v>
+        <v>-0.1501</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7431</v>
+        <v>0.7375</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7431</v>
+        <v>0.7375</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7431</v>
+        <v>0.7375</v>
       </c>
       <c r="I42" t="n">
         <v>0.75</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7338</v>
+        <v>0.7202</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2607</v>
+        <v>0.2559</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1249</v>
+        <v>-0.157</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7338</v>
+        <v>0.7202</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7338</v>
+        <v>0.7202</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7338</v>
+        <v>0.7202</v>
       </c>
       <c r="I43" t="n">
         <v>0.751</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6671</v>
+        <v>0.6498</v>
       </c>
       <c r="C44" t="n">
-        <v>0.237</v>
+        <v>0.2309</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1519</v>
+        <v>-0.185</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6671</v>
+        <v>0.6498</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6671</v>
+        <v>0.6498</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6671</v>
+        <v>0.6498</v>
       </c>
       <c r="I44" t="n">
         <v>0.6891</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6458</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2294</v>
+        <v>0.2219</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1605</v>
+        <v>-0.1951</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6458</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6458</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6458</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="I45" t="n">
         <v>0.6734</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6056</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2152</v>
+        <v>0.2104</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1767</v>
+        <v>-0.208</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6056</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6056</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6056</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="I46" t="n">
         <v>0.6227</v>
@@ -2572,7 +2572,7 @@
         <v>0.2033</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1902</v>
+        <v>-0.216</v>
       </c>
       <c r="E47" t="n">
         <v>0.5721000000000001</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5074</v>
+        <v>0.498</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1803</v>
+        <v>0.1769</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2164</v>
+        <v>-0.2455</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5074</v>
+        <v>0.498</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5074</v>
+        <v>0.498</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5074</v>
+        <v>0.498</v>
       </c>
       <c r="I48" t="n">
         <v>0.5193</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.466</v>
+        <v>0.4574</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1656</v>
+        <v>0.1625</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2331</v>
+        <v>-0.2617</v>
       </c>
       <c r="E49" t="n">
-        <v>0.466</v>
+        <v>0.4574</v>
       </c>
       <c r="F49" t="n">
-        <v>0.466</v>
+        <v>0.4574</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.466</v>
+        <v>0.4574</v>
       </c>
       <c r="I49" t="n">
         <v>0.477</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.3033</v>
+        <v>0.2977</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1078</v>
+        <v>0.1058</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2988</v>
+        <v>-0.3253</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3033</v>
+        <v>0.2977</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3033</v>
+        <v>0.2977</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3033</v>
+        <v>0.2977</v>
       </c>
       <c r="I50" t="n">
         <v>0.3104</v>
@@ -2756,7 +2756,7 @@
         <v>0.1051</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3019</v>
+        <v>-0.3261</v>
       </c>
       <c r="E51" t="n">
         <v>0.2957</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.2663</v>
+        <v>0.2643</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0946</v>
+        <v>0.0939</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3138</v>
+        <v>-0.3386</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2663</v>
+        <v>0.2643</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2663</v>
+        <v>0.2643</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2663</v>
+        <v>0.2643</v>
       </c>
       <c r="I52" t="n">
         <v>0.2688</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.219</v>
+        <v>0.2149</v>
       </c>
       <c r="C53" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3329</v>
+        <v>-0.3583</v>
       </c>
       <c r="E53" t="n">
-        <v>0.219</v>
+        <v>0.2149</v>
       </c>
       <c r="F53" t="n">
-        <v>0.219</v>
+        <v>0.2149</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.219</v>
+        <v>0.2149</v>
       </c>
       <c r="I53" t="n">
         <v>0.2241</v>
@@ -2894,7 +2894,7 @@
         <v>0.0617</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3512</v>
+        <v>-0.3747</v>
       </c>
       <c r="E54" t="n">
         <v>0.1738</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.102</v>
+        <v>0.1016</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0362</v>
+        <v>0.0361</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3802</v>
+        <v>-0.4034</v>
       </c>
       <c r="E55" t="n">
-        <v>0.102</v>
+        <v>0.1016</v>
       </c>
       <c r="F55" t="n">
-        <v>0.102</v>
+        <v>0.1016</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.102</v>
+        <v>0.1016</v>
       </c>
       <c r="I55" t="n">
         <v>0.1025</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.0858</v>
+        <v>0.0842</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0305</v>
+        <v>0.0299</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.3867</v>
+        <v>-0.4104</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0858</v>
+        <v>0.0842</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0858</v>
+        <v>0.0842</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0858</v>
+        <v>0.0842</v>
       </c>
       <c r="I56" t="n">
         <v>0.0878</v>
@@ -3032,7 +3032,7 @@
         <v>-0.009900000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4327</v>
+        <v>-0.4551</v>
       </c>
       <c r="E57" t="n">
         <v>-0.028</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.1306</v>
+        <v>-0.1301</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0464</v>
+        <v>-0.0462</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4741</v>
+        <v>-0.4957</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1306</v>
+        <v>-0.1301</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1306</v>
+        <v>-0.1301</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.1306</v>
+        <v>-0.1301</v>
       </c>
       <c r="I58" t="n">
         <v>-0.1312</v>
@@ -3124,7 +3124,7 @@
         <v>-0.0516</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.48</v>
+        <v>-0.5018</v>
       </c>
       <c r="E59" t="n">
         <v>-0.1452</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.2</v>
+        <v>-0.1955</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0711</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5022</v>
+        <v>-0.5218</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.2</v>
+        <v>-0.1955</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2</v>
+        <v>-0.1955</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.2</v>
+        <v>-0.1955</v>
       </c>
       <c r="I60" t="n">
         <v>-0.2056</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.2086</v>
+        <v>-0.201</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0741</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5056</v>
+        <v>-0.524</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2086</v>
+        <v>-0.201</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.2086</v>
+        <v>-0.201</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.2086</v>
+        <v>-0.201</v>
       </c>
       <c r="I61" t="n">
         <v>-0.2186</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.2624</v>
+        <v>-0.2566</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0912</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5274</v>
+        <v>-0.5461</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.2624</v>
+        <v>-0.2566</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2624</v>
+        <v>-0.2566</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.2624</v>
+        <v>-0.2566</v>
       </c>
       <c r="I62" t="n">
         <v>-0.2698</v>
@@ -3308,7 +3308,7 @@
         <v>-0.1237</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.5826</v>
       </c>
       <c r="E63" t="n">
         <v>-0.3482</v>
@@ -3348,25 +3348,25 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.4332</v>
+        <v>-0.4316</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1539</v>
+        <v>-0.1533</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.5964</v>
+        <v>-0.6159</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4332</v>
+        <v>-0.4316</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.4332</v>
+        <v>-0.4316</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.4332</v>
+        <v>-0.4316</v>
       </c>
       <c r="I64" t="n">
         <v>-0.4352</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.4864</v>
+        <v>-0.4846</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1728</v>
+        <v>-0.1722</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6179</v>
+        <v>-0.637</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.4864</v>
+        <v>-0.4846</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.4864</v>
+        <v>-0.4846</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.4864</v>
+        <v>-0.4846</v>
       </c>
       <c r="I65" t="n">
         <v>-0.4887</v>
@@ -3446,7 +3446,7 @@
         <v>-0.1936</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6415</v>
+        <v>-0.661</v>
       </c>
       <c r="E66" t="n">
         <v>-0.545</v>
@@ -3492,7 +3492,7 @@
         <v>-0.2215</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.6733</v>
+        <v>-0.6924</v>
       </c>
       <c r="E67" t="n">
         <v>-0.6236</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.901</v>
+        <v>-0.8943</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3201</v>
+        <v>-0.3177</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7853</v>
+        <v>-0.8002</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.901</v>
+        <v>-0.8943</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.901</v>
+        <v>-0.8943</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.901</v>
+        <v>-0.8943</v>
       </c>
       <c r="I68" t="n">
         <v>-0.9094</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.9673</v>
+        <v>-0.9458</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3437</v>
+        <v>-0.336</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8121</v>
+        <v>-0.8207</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.9673</v>
+        <v>-0.9458</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.9673</v>
+        <v>-0.9458</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.9673</v>
+        <v>-0.9458</v>
       </c>
       <c r="I69" t="n">
         <v>-0.9946</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.233</v>
+        <v>-1.2056</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.438</v>
+        <v>-0.4283</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9195</v>
+        <v>-0.9242</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.233</v>
+        <v>-1.2056</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.233</v>
+        <v>-1.2056</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.233</v>
+        <v>-1.2056</v>
       </c>
       <c r="I70" t="n">
         <v>-1.2678</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.2617</v>
+        <v>-1.2337</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4482</v>
+        <v>-0.4383</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9311</v>
+        <v>-0.9354</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.2617</v>
+        <v>-1.2337</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.2617</v>
+        <v>-1.2337</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.2617</v>
+        <v>-1.2337</v>
       </c>
       <c r="I71" t="n">
         <v>-1.2973</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.3843</v>
+        <v>-1.3587</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4918</v>
+        <v>-0.4827</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9806</v>
+        <v>-0.9852</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3843</v>
+        <v>-1.3587</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.3843</v>
+        <v>-1.3587</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.3843</v>
+        <v>-1.3587</v>
       </c>
       <c r="I72" t="n">
         <v>-1.4168</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.5161</v>
+        <v>-1.5048</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5386</v>
+        <v>-0.5346</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0338</v>
+        <v>-1.0434</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.5161</v>
+        <v>-1.5048</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.5161</v>
+        <v>-1.5048</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.5161</v>
+        <v>-1.5048</v>
       </c>
       <c r="I73" t="n">
         <v>-1.5302</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.9293</v>
+        <v>-1.8936</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6854</v>
+        <v>-0.6727</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2008</v>
+        <v>-1.1983</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.9293</v>
+        <v>-1.8936</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.9293</v>
+        <v>-1.8936</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.9293</v>
+        <v>-1.8936</v>
       </c>
       <c r="I74" t="n">
         <v>-1.9746</v>
@@ -3850,53 +3850,53 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Kyojin</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-2</v>
+        <v>-1.9917</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7105</v>
+        <v>-0.7076</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2293</v>
+        <v>-1.2374</v>
       </c>
       <c r="E75" t="n">
-        <v>-2</v>
+        <v>-1.9917</v>
       </c>
       <c r="F75" t="n">
-        <v>-2</v>
+        <v>-1.9917</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-2</v>
+        <v>-1.9917</v>
       </c>
       <c r="I75" t="n">
-        <v>-2</v>
+        <v>-2.0944</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>98</v>
+        <v>281</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-2</v>
+        <v>-2.0944</v>
       </c>
       <c r="N75" t="n">
-        <v>98</v>
+        <v>281</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3906,7 +3906,7 @@
         <v>-0.7105</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E76" t="n">
         <v>-2</v>
@@ -3942,47 +3942,47 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Kyojin</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.0369</v>
+        <v>-2</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7237</v>
+        <v>-0.7105</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2442</v>
+        <v>-1.2407</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.0369</v>
+        <v>-2</v>
       </c>
       <c r="F77" t="n">
-        <v>-2.0369</v>
+        <v>-2</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-2.0369</v>
+        <v>-2</v>
       </c>
       <c r="I77" t="n">
-        <v>-2.0944</v>
+        <v>-2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>281</v>
+        <v>98</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-2.0944</v>
+        <v>-2</v>
       </c>
       <c r="N77" t="n">
-        <v>281</v>
+        <v>98</v>
       </c>
     </row>
     <row r="78">
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.4814</v>
+        <v>-2.4173</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.8588</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4238</v>
+        <v>-1.407</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.4814</v>
+        <v>-2.4173</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.4814</v>
+        <v>-2.4173</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.4814</v>
+        <v>-2.4173</v>
       </c>
       <c r="I78" t="n">
         <v>-2.5634</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.6318</v>
+        <v>-2.5447</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.9041</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4846</v>
+        <v>-1.4577</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.6318</v>
+        <v>-2.5447</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.6318</v>
+        <v>-2.5447</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.6318</v>
+        <v>-2.5447</v>
       </c>
       <c r="I79" t="n">
         <v>-2.7441</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.6052</v>
+        <v>-3.5385</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.2808</v>
+        <v>-1.2571</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.8778</v>
+        <v>-1.8536</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.6052</v>
+        <v>-3.5385</v>
       </c>
       <c r="F80" t="n">
-        <v>-3.6052</v>
+        <v>-3.5385</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-3.6052</v>
+        <v>-3.5385</v>
       </c>
       <c r="I80" t="n">
         <v>-3.6899</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.3339</v>
+        <v>-4.1438</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.5397</v>
+        <v>-1.4722</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.1722</v>
+        <v>-2.0948</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.3339</v>
+        <v>-4.1438</v>
       </c>
       <c r="F81" t="n">
-        <v>-4.3339</v>
+        <v>-4.1438</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-4.3339</v>
+        <v>-4.1438</v>
       </c>
       <c r="I81" t="n">
         <v>-4.5822</v>
